--- a/Result/profitability/4131.xlsx
+++ b/Result/profitability/4131.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.16</v>
+        <v>-0.1175</v>
       </c>
       <c r="N2" t="n">
-        <v>39.8675</v>
+        <v>42.45625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.11375</v>
+        <v>-0.105</v>
       </c>
       <c r="N3" t="n">
-        <v>46.5375</v>
+        <v>49.25</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.095</v>
+        <v>-0.05875</v>
       </c>
       <c r="N4" t="n">
-        <v>53.0025</v>
+        <v>53.42750000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>-0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06375</v>
+        <v>-0.105</v>
       </c>
       <c r="N5" t="n">
-        <v>62.17875000000001</v>
+        <v>62.535</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1225</v>
+        <v>-0.0725</v>
       </c>
       <c r="N6" t="n">
-        <v>64.18625</v>
+        <v>64.86625000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.10125</v>
+        <v>-0.06</v>
       </c>
       <c r="N7" t="n">
-        <v>67.97</v>
+        <v>68.535</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0775</v>
+        <v>-0.07375</v>
       </c>
       <c r="N8" t="n">
-        <v>73.30249999999999</v>
+        <v>71.88249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.1125</v>
       </c>
       <c r="N11" t="n">
-        <v>72.29125000000001</v>
+        <v>72.29124999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.14</v>
       </c>
       <c r="N12" t="n">
-        <v>72.22500000000001</v>
+        <v>72.22499999999999</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>96</v>
+      </c>
+      <c r="D75" t="n">
+        <v>58</v>
+      </c>
+      <c r="E75" t="n">
+        <v>38</v>
+      </c>
+      <c r="F75" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.65%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.16125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.4725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-11.36</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2238864800945999</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.064516129032258</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.850000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07801806734191086</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
